--- a/branches/pt/CodeSystem-edqm-route-cs.xlsx
+++ b/branches/pt/CodeSystem-edqm-route-cs.xlsx
@@ -37,7 +37,7 @@
     <t>Name</t>
   </si>
   <si>
-    <t>EDQM-ROUTE-CS</t>
+    <t>EDQM_ROUTE_CS</t>
   </si>
   <si>
     <t>Title</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-08-24T21:33:25+00:00</t>
+    <t>2022-08-29T19:31:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
